--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3804,8 +3804,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61E6756D-B432-4674-859D-7BDCBEC9364C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC309923-FF6B-4B60-84B1-2F36A5DD622A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781E422D-097E-43F4-9E05-CEEAB81AB24F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE545D94-D3DB-4E4C-B4E9-0AC911C5E892}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53D370DE-66ED-44E4-990D-6CDAA8FD58BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{722C99C1-D418-4092-9983-2E091F12760B}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC309923-FF6B-4B60-84B1-2F36A5DD622A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3514A1E3-D8CB-4410-8969-AA7F5A4E874D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE545D94-D3DB-4E4C-B4E9-0AC911C5E892}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC78CC46-86BB-443A-B0C8-4C034CCDB2D2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{722C99C1-D418-4092-9983-2E091F12760B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD14D1C7-2198-4FA9-BB55-73159305D048}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3514A1E3-D8CB-4410-8969-AA7F5A4E874D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CCB3DD7-3D32-40DB-B829-6211AEB2C9B0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC78CC46-86BB-443A-B0C8-4C034CCDB2D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C675992-12DA-4F27-8585-66240434C304}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD14D1C7-2198-4FA9-BB55-73159305D048}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26ABA72D-F24A-45AF-90D2-8DDD63F0CFAD}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CCB3DD7-3D32-40DB-B829-6211AEB2C9B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A023D272-D1DF-4676-B50E-AEFCA681BE2E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C675992-12DA-4F27-8585-66240434C304}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1245656D-A806-4F27-A6C8-76D1D63F0792}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26ABA72D-F24A-45AF-90D2-8DDD63F0CFAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{842E5D9E-6F12-4170-95BB-98ECE35B4FE3}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A023D272-D1DF-4676-B50E-AEFCA681BE2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E44CE42-8525-41B8-9726-CFBCBB299B8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1245656D-A806-4F27-A6C8-76D1D63F0792}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF120D6C-334B-469F-9264-8324A63E2AA2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{842E5D9E-6F12-4170-95BB-98ECE35B4FE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E96BF6DB-3F20-4433-BF7A-C5D809F37061}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E44CE42-8525-41B8-9726-CFBCBB299B8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8A4B39D-37A9-47A0-B4A4-846C115DC97C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF120D6C-334B-469F-9264-8324A63E2AA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4697577D-AEE2-4629-8EDA-66678F4AE634}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E96BF6DB-3F20-4433-BF7A-C5D809F37061}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04390FEA-BA99-4272-B50E-754963C1801A}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8A4B39D-37A9-47A0-B4A4-846C115DC97C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0640B649-5838-4A9A-B6F7-17684F90F1EB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4697577D-AEE2-4629-8EDA-66678F4AE634}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3460319D-05BE-4274-A71F-8983199D5652}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04390FEA-BA99-4272-B50E-754963C1801A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B3A1BFB-ECEB-40B7-9B9E-F924CC003F3D}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0640B649-5838-4A9A-B6F7-17684F90F1EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A3CFD1-EB65-45D1-98F7-A2EB2F16E7CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3460319D-05BE-4274-A71F-8983199D5652}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F8E11F6-EA96-452E-9421-25E339B81730}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B3A1BFB-ECEB-40B7-9B9E-F924CC003F3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81EFB92C-4CFA-4756-93A6-A53912DE4E9E}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A3CFD1-EB65-45D1-98F7-A2EB2F16E7CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AEBF73-9766-4CE5-848C-E6F06C6351BF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F8E11F6-EA96-452E-9421-25E339B81730}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{833E5DD1-F93C-477F-9F93-9C2CC1FC81C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81EFB92C-4CFA-4756-93A6-A53912DE4E9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABEA69CD-3417-4B71-A2D7-5D3821E3FB89}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AEBF73-9766-4CE5-848C-E6F06C6351BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D9556FF-41FA-4B4C-88AB-66739F2D3269}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{833E5DD1-F93C-477F-9F93-9C2CC1FC81C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D5B3E91-A11A-4AED-802C-FFB0D530355C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABEA69CD-3417-4B71-A2D7-5D3821E3FB89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C911B48-B7E9-4CBC-B775-2DD3B1D4C4D8}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D9556FF-41FA-4B4C-88AB-66739F2D3269}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8D1738A-5CC3-463D-8041-42ABCC861C34}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D5B3E91-A11A-4AED-802C-FFB0D530355C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8B0BC68-AA51-414A-8797-8D66A08A2855}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C911B48-B7E9-4CBC-B775-2DD3B1D4C4D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB867BE6-2F54-4B6C-A37D-B47184308502}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8D1738A-5CC3-463D-8041-42ABCC861C34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7647A12F-A90D-40F1-A589-AFCFE91206B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8B0BC68-AA51-414A-8797-8D66A08A2855}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522A6CBF-FD2C-48CE-BC61-E8CF8D28CD59}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB867BE6-2F54-4B6C-A37D-B47184308502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{155AC1F0-6171-410B-8246-5C710D949612}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7647A12F-A90D-40F1-A589-AFCFE91206B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A35373D-5B91-49BD-9976-86D66B04771A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522A6CBF-FD2C-48CE-BC61-E8CF8D28CD59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5898CBD6-1A0A-42A6-B89C-29A45B77DE6E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{155AC1F0-6171-410B-8246-5C710D949612}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73C54FC9-0248-4A48-B198-E43F1FF7A27E}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A35373D-5B91-49BD-9976-86D66B04771A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18ADBE08-1F60-40BF-B6E1-1BF2AB18668B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5898CBD6-1A0A-42A6-B89C-29A45B77DE6E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09C762D-872B-4464-ABD4-943E395290F6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73C54FC9-0248-4A48-B198-E43F1FF7A27E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A03FC9E-0B43-45ED-888F-25BFDC445B19}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18ADBE08-1F60-40BF-B6E1-1BF2AB18668B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ABCE2DE-7501-4474-8A8D-AC0852571062}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09C762D-872B-4464-ABD4-943E395290F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79E46B29-E226-46AD-A998-D7E4D61C6699}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A03FC9E-0B43-45ED-888F-25BFDC445B19}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05F294F6-7898-41D4-8D1C-9F8C78468A7E}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3801,291 +3801,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EEF7463-274A-4A85-9126-16DB61FBF1A9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B872F2AF-932F-4ABC-AD67-FFED45E70AC5}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{860AC6EA-37F7-43BA-92EA-2E80523E3F54}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3801,4 +3801,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B621154-9D14-4C9D-926A-9B366075BBDE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40277D2F-78B9-4711-8FF8-64F57ABF4489}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{579369CC-2F27-4483-BCC1-118666D2EE46}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B621154-9D14-4C9D-926A-9B366075BBDE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{543921AA-666F-4FEA-94FC-51405D51797E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40277D2F-78B9-4711-8FF8-64F57ABF4489}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A3E96F-1F10-4E29-803C-F03093C5C411}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{579369CC-2F27-4483-BCC1-118666D2EE46}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B15C2B-1310-4914-BCB9-136BC1AAA495}"/>
 </file>